--- a/assets_management/tests/data/account_fiscal_year.xlsx
+++ b/assets_management/tests/data/account_fiscal_year.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="account.account_test" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="account.account_test" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -34,19 +34,64 @@
     <t xml:space="preserve">date_to</t>
   </si>
   <si>
-    <t xml:space="preserve">z0bug.year_2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.year_2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.year_2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.year_2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0bug.year_2020</t>
+    <t xml:space="preserve">z0bug.year+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;?odoo compute_date('###&gt;-##-##')[0:4] ?&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">###&gt;-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">###&gt;-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.year_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;?odoo compute_date('####-##-##')[0:4] ?&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">####-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">####-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.year-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;?odoo compute_date('&lt;0001-##-##')[0:4] ?&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;001-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;001-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.year-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;?odoo compute_date('&lt;0002-##-##')[0:4] ?&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;002-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;002-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z0bug.year-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;?odoo compute_date('&lt;0003-##-##')[0:4] ?&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;003-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;003-12-31</t>
   </si>
 </sst>
 </file>
@@ -135,7 +180,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -151,6 +196,112 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -159,8 +310,8 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.47"/>
   </cols>
@@ -183,70 +334,70 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>45292</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>45657</v>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>44927</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>45291</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>44562</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>44926</v>
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>44197</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>44561</v>
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>43831</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>44196</v>
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
